--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.47131182793699</v>
+        <v>4.139088172039761</v>
       </c>
       <c r="D2" t="n">
-        <v>25.44403274156478</v>
+        <v>4.134655320504277</v>
       </c>
       <c r="E2" t="n">
-        <v>12.23676537162284</v>
+        <v>1.988474372888711</v>
       </c>
       <c r="F2" t="n">
-        <v>12.24073203581754</v>
+        <v>1.989118955820351</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.12617644213668</v>
+        <v>3.920503671847211</v>
       </c>
       <c r="D3" t="n">
-        <v>24.43861002349294</v>
+        <v>3.971274128817603</v>
       </c>
       <c r="E3" t="n">
-        <v>12.23676537162284</v>
+        <v>1.988474372888711</v>
       </c>
       <c r="F3" t="n">
-        <v>12.24073203581754</v>
+        <v>1.989118955820351</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.49186792000181</v>
+        <v>7.717428537000294</v>
       </c>
       <c r="D4" t="n">
-        <v>47.08984363619503</v>
+        <v>7.652099590881694</v>
       </c>
       <c r="E4" t="n">
-        <v>12.23676537162284</v>
+        <v>1.988474372888711</v>
       </c>
       <c r="F4" t="n">
-        <v>12.24073203581754</v>
+        <v>1.989118955820351</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.7776932364353</v>
+        <v>2.076375150920736</v>
       </c>
       <c r="D5" t="n">
-        <v>11.86982329132396</v>
+        <v>1.928846284840143</v>
       </c>
       <c r="E5" t="n">
-        <v>12.23676537162284</v>
+        <v>1.988474372888711</v>
       </c>
       <c r="F5" t="n">
-        <v>12.24073203581754</v>
+        <v>1.989118955820351</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.46537783277245</v>
+        <v>1.700623897825523</v>
       </c>
       <c r="D6" t="n">
-        <v>9.988247509982704</v>
+        <v>1.62309022037219</v>
       </c>
       <c r="E6" t="n">
-        <v>12.23676537162284</v>
+        <v>1.988474372888711</v>
       </c>
       <c r="F6" t="n">
-        <v>12.24073203581754</v>
+        <v>1.989118955820351</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.57290921351414</v>
+        <v>4.968097747196048</v>
       </c>
       <c r="D7" t="n">
-        <v>28.71356662234444</v>
+        <v>4.665954576130972</v>
       </c>
       <c r="E7" t="n">
-        <v>12.23676537162284</v>
+        <v>1.988474372888711</v>
       </c>
       <c r="F7" t="n">
-        <v>12.24073203581754</v>
+        <v>1.989118955820351</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
